--- a/medical_surveys_questionnaires/038_dermatological_products_knowledge_quiz--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/038_dermatological_products_knowledge_quiz--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,40 +515,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>skin_types</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>Skin Types</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>skin_types</t>
+          <t>skin_concerns</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>skin_types</t>
+          <t>Skin Concerns</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,24 +561,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>skin_concerns</t>
+          <t>skin_products</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>skin_concerns</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>What are you concerned about with your skin?</t>
-        </is>
-      </c>
+          <t>Skin Products</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -588,24 +584,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>skin_products</t>
+          <t>dermatology_questions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>skin_products</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>What skin product do you use?</t>
-        </is>
-      </c>
+          <t>Dermatological Questions</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -615,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dermatology_questions</t>
+          <t>skincare_expert_contact</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dermatology_questions</t>
+          <t>Skincare Expert Contact Information</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -643,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>skincare_expert</t>
+          <t>relationship_with_skincare_expert</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>skincare_expert</t>
+          <t>Relationship with Skincare Expert</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -666,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>skincare_expert_phone</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>skincare_expert_phone</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -689,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>skincare_form_comments</t>
+          <t>comments2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>skincare_form_comments</t>
+          <t>Comments2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -712,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>skincare_form_comments2</t>
+          <t>comments3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>skincare_form_comments</t>
+          <t>Comments3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -735,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>skincare_expert_signature</t>
+          <t>comments4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>skincare_expert_signature</t>
+          <t>Comments4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -758,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>skincare_expert_signature2</t>
+          <t>comments5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>skincare_expert_signature</t>
+          <t>Comments5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -781,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>skincare_expert_signature3</t>
+          <t>comments6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>skincare_expert_signature</t>
+          <t>Comments6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
